--- a/data/dados_2026.xlsx
+++ b/data/dados_2026.xlsx
@@ -409,16 +409,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -426,10 +429,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="str">
         <v>Sim</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Sim</v>
       </c>
     </row>
@@ -437,10 +443,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="str">
         <v>Sim</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Sim</v>
       </c>
     </row>
@@ -448,10 +457,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="str">
         <v>Sim</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>Sim</v>
       </c>
     </row>
@@ -459,10 +471,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" t="str">
         <v>Sim</v>
       </c>
-      <c r="C5" t="str">
+      <c r="D5" t="str">
         <v>Sim</v>
       </c>
     </row>
@@ -470,32 +485,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Sim</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
         <v>Sim</v>
       </c>
+      <c r="D6" t="str">
+        <v>Sim</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -503,10 +524,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -514,10 +538,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -525,10 +552,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -536,10 +566,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -547,32 +580,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -580,10 +619,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -591,10 +633,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -602,10 +647,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -613,10 +661,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -624,32 +675,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -657,10 +714,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -668,10 +728,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -679,10 +742,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -690,10 +756,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -701,16 +770,19 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -871,16 +943,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -888,10 +963,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -899,10 +977,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -910,10 +991,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -921,10 +1005,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -932,32 +1019,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -965,10 +1058,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -976,10 +1072,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -987,10 +1086,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -998,10 +1100,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1009,32 +1114,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1042,10 +1153,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1053,10 +1167,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1064,10 +1181,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1075,10 +1195,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1086,32 +1209,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1119,10 +1248,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1130,10 +1262,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1141,10 +1276,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1152,10 +1290,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1163,32 +1304,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1196,10 +1343,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1207,10 +1357,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1218,10 +1371,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1229,10 +1385,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1240,32 +1399,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1273,10 +1438,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1284,10 +1452,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1295,10 +1466,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1306,10 +1480,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1317,32 +1494,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1350,10 +1533,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1361,10 +1547,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1372,10 +1561,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1383,10 +1575,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1394,32 +1589,38 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Nome</v>
       </c>
       <c r="B1" t="str">
+        <v>Quantidade de Pessoas</v>
+      </c>
+      <c r="C1" t="str">
         <v>Pagamento Água</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Pagamento Luz</v>
       </c>
     </row>
@@ -1427,10 +1628,13 @@
       <c r="A2" t="str">
         <v>Apartamento 101</v>
       </c>
-      <c r="B2" t="str">
-        <v>Não</v>
+      <c r="B2">
+        <v>1</v>
       </c>
       <c r="C2" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D2" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1438,10 +1642,13 @@
       <c r="A3" t="str">
         <v>Apartamento 102</v>
       </c>
-      <c r="B3" t="str">
-        <v>Não</v>
+      <c r="B3">
+        <v>1</v>
       </c>
       <c r="C3" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D3" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1449,10 +1656,13 @@
       <c r="A4" t="str">
         <v>Apartamento 103</v>
       </c>
-      <c r="B4" t="str">
-        <v>Não</v>
+      <c r="B4">
+        <v>1</v>
       </c>
       <c r="C4" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D4" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1460,10 +1670,13 @@
       <c r="A5" t="str">
         <v>Apartamento 201</v>
       </c>
-      <c r="B5" t="str">
-        <v>Não</v>
+      <c r="B5">
+        <v>1</v>
       </c>
       <c r="C5" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D5" t="str">
         <v>Não</v>
       </c>
     </row>
@@ -1471,16 +1684,19 @@
       <c r="A6" t="str">
         <v>Apartamento 202</v>
       </c>
-      <c r="B6" t="str">
-        <v>Não</v>
+      <c r="B6">
+        <v>1</v>
       </c>
       <c r="C6" t="str">
+        <v>Não</v>
+      </c>
+      <c r="D6" t="str">
         <v>Não</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>